--- a/artfynd/A 21966-2022 artfynd.xlsx
+++ b/artfynd/A 21966-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21966-2022 artfynd.xlsx
+++ b/artfynd/A 21966-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100210483</v>
+        <v>100210494</v>
       </c>
       <c r="B2" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223246</v>
+        <v>219862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616573.1766451874</v>
+        <v>616573</v>
       </c>
       <c r="R2" t="n">
-        <v>6594723.678015481</v>
+        <v>6594724</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1980-05-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1980-07-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,12 +780,7 @@
         <v>100210492</v>
       </c>
       <c r="B3" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616573.1766451874</v>
+        <v>616573</v>
       </c>
       <c r="R3" t="n">
-        <v>6594723.678015481</v>
+        <v>6594724</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,19 +845,9 @@
           <t>1980-05-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1980-07-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100210494</v>
+        <v>100210483</v>
       </c>
       <c r="B4" t="n">
-        <v>96355</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219862</v>
+        <v>223246</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Huds.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616573.1766451874</v>
+        <v>616573</v>
       </c>
       <c r="R4" t="n">
-        <v>6594723.678015481</v>
+        <v>6594724</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -982,19 +947,9 @@
           <t>1980-05-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1980-07-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 21966-2022 artfynd.xlsx
+++ b/artfynd/A 21966-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100210494</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100210492</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,8 +993,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100210483</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>